--- a/output/pdf_financials_xlsx/MAH.xlsx
+++ b/output/pdf_financials_xlsx/MAH.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.207964</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.018999</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.012721</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.176161</v>
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.000743</v>
+        <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.001466</v>
+        <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0.001577</v>
@@ -2371,13 +2371,13 @@
         <v>-3.996795</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.138211</v>
+        <v>-0.03795</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.252029</v>
+        <v>-3.252772</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.60495</v>
+        <v>-1.606416</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.933474</v>
@@ -2441,10 +2441,10 @@
         <v>-651.7441613968946</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>39.83944425227718</v>
+        <v>-10.93912141127637</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-8343.884541372676</v>
+        <v>-8345.790891597177</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -6531,16 +6531,16 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0.176161</v>
+        <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0.000743</v>
+        <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.001466</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0.001577</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3" t="n">
         <v>0</v>
@@ -7584,10 +7584,10 @@
         <v>0</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.222061</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.756514</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0</v>
@@ -45396,7 +45396,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -46875,7 +46879,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -71400,15 +71404,19 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E633" s="5" t="n">
-        <v>-0.207964</v>
+        <v>0.207964</v>
       </c>
       <c r="F633" s="5" t="n">
-        <v>-0.018999</v>
+        <v>0.018999</v>
       </c>
       <c r="G633" s="5" t="n">
-        <v>-0.012721</v>
+        <v>0.012721</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MAH.xlsx
+++ b/output/pdf_financials_xlsx/MAH.xlsx
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.020988</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000301</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.213311</v>
+        <v>-1.234299</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.996795</v>
+        <v>-3.997096</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.03795</v>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.176161</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.000743</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.001466</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0.001577</v>
@@ -2365,19 +2365,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.213311</v>
+        <v>-1.234299</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.996795</v>
+        <v>-3.997096</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.03795</v>
+        <v>0.138211</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.252772</v>
+        <v>-3.252029</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.606416</v>
+        <v>-1.60495</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.933474</v>
@@ -2435,16 +2435,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-68.20358019174179</v>
+        <v>-69.38337394706443</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-651.7441613968946</v>
+        <v>-651.7932444728543</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-10.93912141127637</v>
+        <v>39.83944425227718</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-8345.790891597177</v>
+        <v>-8343.884541372676</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -2681,34 +2681,34 @@
         <v>0.09615</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.138987</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.116806</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.8010969999999999</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.107685</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.113203</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.621413</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.338319</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.088938</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.088795</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.242876</v>
       </c>
     </row>
     <row r="35">
@@ -2797,34 +2797,34 @@
         <v>0.09615</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.138987</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.116806</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.8010969999999999</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.107685</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.113203</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.621413</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.338319</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.088938</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.088795</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.242876</v>
       </c>
     </row>
     <row r="37">
@@ -3493,34 +3493,34 @@
         <v>0.16629</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.266428</v>
+        <v>0.127441</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.176378</v>
+        <v>0.059572</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.860955</v>
+        <v>0.059858</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.169825</v>
+        <v>0.06214</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.175217</v>
+        <v>0.062014</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.683509</v>
+        <v>0.062096</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.402571</v>
+        <v>0.064252</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.245276</v>
+        <v>0.156338</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.158729</v>
+        <v>0.069934</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.313244</v>
+        <v>0.070368</v>
       </c>
     </row>
     <row r="49">
@@ -6531,16 +6531,16 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.176161</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.000743</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.001466</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.001577</v>
       </c>
       <c r="H100" s="3" t="n">
         <v>0</v>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -46879,7 +46879,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -54192,7 +54192,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -56366,7 +56366,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -58170,7 +58170,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -60754,7 +60754,7 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -62657,7 +62657,7 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -73202,7 +73202,7 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E651" s="5" t="n">

--- a/output/pdf_financials_xlsx/MAH.xlsx
+++ b/output/pdf_financials_xlsx/MAH.xlsx
@@ -1205,16 +1205,16 @@
         <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>0.510421</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>0.113598</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>0.198986</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>0.079802</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>-0</v>
@@ -2231,16 +2231,16 @@
         <v>-3.997096</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.03795</v>
+        <v>-0.5483710000000001</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.252772</v>
+        <v>-3.36637</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.606416</v>
+        <v>-1.805402</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.935051</v>
+        <v>-1.014853</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.939297</v>
@@ -2371,16 +2371,16 @@
         <v>-3.997096</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.138211</v>
+        <v>-0.37221</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.252029</v>
+        <v>-3.365627</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.60495</v>
+        <v>-1.803936</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.933474</v>
+        <v>-1.013276</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.830977</v>
@@ -2441,10 +2441,10 @@
         <v>-651.7932444728543</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>39.83944425227718</v>
+        <v>-107.2898650985818</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-8343.884541372676</v>
+        <v>-8635.348300192432</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -7221,13 +7221,13 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>1.02451</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -51079,7 +51079,11 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
           <t>-</t>
@@ -52303,7 +52307,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E442" s="5" t="n">
         <v>1.02451</v>
       </c>
@@ -63160,7 +63168,11 @@
           <t>Net financing expenses</t>
         </is>
       </c>
-      <c r="D551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E551" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MAH.xlsx
+++ b/output/pdf_financials_xlsx/MAH.xlsx
@@ -1485,7 +1485,7 @@
         <v>0.669472</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.009976</v>
+        <v>-0.009976</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -7227,7 +7227,7 @@
         <v>0.225</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -42222,7 +42222,11 @@
           <t>Future income tax recovery (note 12)</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -43212,7 +43216,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -44709,7 +44717,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -48869,7 +48881,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
@@ -50384,7 +50400,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E423" s="5" t="n">
         <v>-0.238574</v>
       </c>
@@ -51079,11 +51099,7 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>SaleOfPPE</t>
-        </is>
-      </c>
+      <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
           <t>-</t>
@@ -70911,7 +70927,11 @@
           <t>Deferred income tax recovery (note 12)</t>
         </is>
       </c>
-      <c r="D628" t="inlineStr"/>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E628" t="inlineStr">
         <is>
           <t>-</t>
